--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N28_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N28_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.43592673562118</v>
+        <v>5.433338094538442</v>
       </c>
       <c r="D2" t="n">
-        <v>32.92192242337708</v>
+        <v>5.349812393798775</v>
       </c>
       <c r="E2" t="n">
-        <v>25.93019359112659</v>
+        <v>4.21365645855807</v>
       </c>
       <c r="F2" t="n">
-        <v>25.82508850610065</v>
+        <v>4.196576882241356</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>59.92419000015424</v>
+        <v>9.737680875025065</v>
       </c>
       <c r="D3" t="n">
-        <v>59.2196299883029</v>
+        <v>9.623189873099221</v>
       </c>
       <c r="E3" t="n">
-        <v>25.93019359112659</v>
+        <v>4.21365645855807</v>
       </c>
       <c r="F3" t="n">
-        <v>25.82508850610065</v>
+        <v>4.196576882241356</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>8.156597342454758</v>
+        <v>1.325447068148898</v>
       </c>
       <c r="D4" t="n">
-        <v>8.264790603214015</v>
+        <v>1.343028473022277</v>
       </c>
       <c r="E4" t="n">
-        <v>25.93019359112659</v>
+        <v>4.21365645855807</v>
       </c>
       <c r="F4" t="n">
-        <v>25.82508850610065</v>
+        <v>4.196576882241356</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>35.96075389888211</v>
+        <v>5.843622508568343</v>
       </c>
       <c r="D5" t="n">
-        <v>36.70836556649178</v>
+        <v>5.965109404554914</v>
       </c>
       <c r="E5" t="n">
-        <v>25.93019359112659</v>
+        <v>4.21365645855807</v>
       </c>
       <c r="F5" t="n">
-        <v>25.82508850610065</v>
+        <v>4.196576882241356</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>84.59775293898912</v>
+        <v>13.74713485258573</v>
       </c>
       <c r="D6" t="n">
-        <v>84.62942677728725</v>
+        <v>13.75228185130918</v>
       </c>
       <c r="E6" t="n">
-        <v>25.93019359112659</v>
+        <v>4.21365645855807</v>
       </c>
       <c r="F6" t="n">
-        <v>25.82508850610065</v>
+        <v>4.196576882241356</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
